--- a/server/data/users.xlsx
+++ b/server/data/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VCcode\dreamawake-lottery\server\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A7C9F6-16D7-40FC-9536-87FB5553089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965DFF68-51DE-4264-AC3F-DE9E63DBC155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4503" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="1705">
   <si>
     <t>工号</t>
   </si>
@@ -4549,6 +4549,606 @@
   </si>
   <si>
     <t>1500</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>1502</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>1505</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>1507</t>
+  </si>
+  <si>
+    <t>1508</t>
+  </si>
+  <si>
+    <t>1509</t>
+  </si>
+  <si>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>1512</t>
+  </si>
+  <si>
+    <t>1513</t>
+  </si>
+  <si>
+    <t>1514</t>
+  </si>
+  <si>
+    <t>1515</t>
+  </si>
+  <si>
+    <t>1516</t>
+  </si>
+  <si>
+    <t>1517</t>
+  </si>
+  <si>
+    <t>1518</t>
+  </si>
+  <si>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>1520</t>
+  </si>
+  <si>
+    <t>1521</t>
+  </si>
+  <si>
+    <t>1522</t>
+  </si>
+  <si>
+    <t>1523</t>
+  </si>
+  <si>
+    <t>1524</t>
+  </si>
+  <si>
+    <t>1525</t>
+  </si>
+  <si>
+    <t>1526</t>
+  </si>
+  <si>
+    <t>1527</t>
+  </si>
+  <si>
+    <t>1528</t>
+  </si>
+  <si>
+    <t>1529</t>
+  </si>
+  <si>
+    <t>1530</t>
+  </si>
+  <si>
+    <t>1531</t>
+  </si>
+  <si>
+    <t>1532</t>
+  </si>
+  <si>
+    <t>1533</t>
+  </si>
+  <si>
+    <t>1534</t>
+  </si>
+  <si>
+    <t>1535</t>
+  </si>
+  <si>
+    <t>1536</t>
+  </si>
+  <si>
+    <t>1537</t>
+  </si>
+  <si>
+    <t>1538</t>
+  </si>
+  <si>
+    <t>1539</t>
+  </si>
+  <si>
+    <t>1540</t>
+  </si>
+  <si>
+    <t>1541</t>
+  </si>
+  <si>
+    <t>1542</t>
+  </si>
+  <si>
+    <t>1543</t>
+  </si>
+  <si>
+    <t>1544</t>
+  </si>
+  <si>
+    <t>1545</t>
+  </si>
+  <si>
+    <t>1546</t>
+  </si>
+  <si>
+    <t>1547</t>
+  </si>
+  <si>
+    <t>1548</t>
+  </si>
+  <si>
+    <t>1549</t>
+  </si>
+  <si>
+    <t>1550</t>
+  </si>
+  <si>
+    <t>1551</t>
+  </si>
+  <si>
+    <t>1552</t>
+  </si>
+  <si>
+    <t>1553</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>1555</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>1557</t>
+  </si>
+  <si>
+    <t>1558</t>
+  </si>
+  <si>
+    <t>1559</t>
+  </si>
+  <si>
+    <t>1560</t>
+  </si>
+  <si>
+    <t>1561</t>
+  </si>
+  <si>
+    <t>1562</t>
+  </si>
+  <si>
+    <t>1563</t>
+  </si>
+  <si>
+    <t>1564</t>
+  </si>
+  <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>1566</t>
+  </si>
+  <si>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>1568</t>
+  </si>
+  <si>
+    <t>1569</t>
+  </si>
+  <si>
+    <t>1570</t>
+  </si>
+  <si>
+    <t>1571</t>
+  </si>
+  <si>
+    <t>1572</t>
+  </si>
+  <si>
+    <t>1573</t>
+  </si>
+  <si>
+    <t>1574</t>
+  </si>
+  <si>
+    <t>1575</t>
+  </si>
+  <si>
+    <t>1576</t>
+  </si>
+  <si>
+    <t>1577</t>
+  </si>
+  <si>
+    <t>1578</t>
+  </si>
+  <si>
+    <t>1579</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>1581</t>
+  </si>
+  <si>
+    <t>1582</t>
+  </si>
+  <si>
+    <t>1583</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>1589</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1613</t>
+  </si>
+  <si>
+    <t>1614</t>
+  </si>
+  <si>
+    <t>1615</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>1632</t>
+  </si>
+  <si>
+    <t>1633</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>1635</t>
+  </si>
+  <si>
+    <t>1636</t>
+  </si>
+  <si>
+    <t>1637</t>
+  </si>
+  <si>
+    <t>1638</t>
+  </si>
+  <si>
+    <t>1639</t>
+  </si>
+  <si>
+    <t>1640</t>
+  </si>
+  <si>
+    <t>1641</t>
+  </si>
+  <si>
+    <t>1642</t>
+  </si>
+  <si>
+    <t>1643</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>1645</t>
+  </si>
+  <si>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>1647</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>1649</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>1651</t>
+  </si>
+  <si>
+    <t>1652</t>
+  </si>
+  <si>
+    <t>1653</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>1655</t>
+  </si>
+  <si>
+    <t>1656</t>
+  </si>
+  <si>
+    <t>1657</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>1659</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>1661</t>
+  </si>
+  <si>
+    <t>1662</t>
+  </si>
+  <si>
+    <t>1663</t>
+  </si>
+  <si>
+    <t>1664</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>1666</t>
+  </si>
+  <si>
+    <t>1667</t>
+  </si>
+  <si>
+    <t>1668</t>
+  </si>
+  <si>
+    <t>1669</t>
+  </si>
+  <si>
+    <t>1670</t>
+  </si>
+  <si>
+    <t>1671</t>
+  </si>
+  <si>
+    <t>1672</t>
+  </si>
+  <si>
+    <t>1673</t>
+  </si>
+  <si>
+    <t>1674</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>1676</t>
+  </si>
+  <si>
+    <t>1677</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>1679</t>
+  </si>
+  <si>
+    <t>1680</t>
+  </si>
+  <si>
+    <t>1681</t>
+  </si>
+  <si>
+    <t>1682</t>
+  </si>
+  <si>
+    <t>1683</t>
+  </si>
+  <si>
+    <t>1684</t>
+  </si>
+  <si>
+    <t>1685</t>
+  </si>
+  <si>
+    <t>1686</t>
+  </si>
+  <si>
+    <t>1687</t>
+  </si>
+  <si>
+    <t>1688</t>
+  </si>
+  <si>
+    <t>1689</t>
+  </si>
+  <si>
+    <t>1690</t>
+  </si>
+  <si>
+    <t>1691</t>
+  </si>
+  <si>
+    <t>1692</t>
+  </si>
+  <si>
+    <t>1693</t>
+  </si>
+  <si>
+    <t>1694</t>
+  </si>
+  <si>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>1696</t>
+  </si>
+  <si>
+    <t>1697</t>
+  </si>
+  <si>
+    <t>1698</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>1700</t>
   </si>
 </sst>
 </file>
@@ -4906,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1501"/>
+  <dimension ref="A1:C1701"/>
   <sheetFormatPr defaultColWidth="26.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="26.75" style="1"/>
@@ -21423,6 +22023,2206 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1502" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1502" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C1502" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1503" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1503" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1503" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1504" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1504" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C1504" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1505" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1505" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C1505" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1506" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1506" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C1506" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1507" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1507" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C1507" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1508" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1508" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C1508" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1509" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1509" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1509" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1510" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1510" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C1510" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1511" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1511" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C1511" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1512" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1512" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C1512" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1513" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1513" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C1513" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1514" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1514" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C1514" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1515" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1515" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C1515" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1516" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1516" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C1516" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1517" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1517" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C1517" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1518" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1518" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C1518" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1519" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1519" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1519" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1520" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1520" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C1520" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1521" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1521" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C1521" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1522" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1522" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C1522" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1523" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1523" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C1523" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1524" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1524" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C1524" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1525" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1525" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1525" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1526" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1526" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C1526" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1527" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1527" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C1527" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1528" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1528" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C1528" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1529" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1529" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C1529" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1530" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1530" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1530" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1531" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1531" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C1531" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1532" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1532" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C1532" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1533" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1533" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C1533" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1534" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1534" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C1534" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1535" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1535" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C1535" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1536" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1536" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C1536" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1537" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1537" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C1537" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1538" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1538" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C1538" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1539" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1539" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C1539" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1540" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1540" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1540" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1541" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1541" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1541" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1542" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1542" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C1542" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1543" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1543" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C1543" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1544" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1544" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C1544" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1545" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1545" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C1545" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1546" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1546" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C1546" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1547" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1547" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C1547" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1548" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1548" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C1548" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1549" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1549" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C1549" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1550" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1550" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C1550" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1551" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1551" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C1551" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1552" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1552" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1552" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1553" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1553" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C1553" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1554" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1554" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C1554" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1555" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1555" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1555" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1556" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1556" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C1556" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1557" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1557" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C1557" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1558" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1558" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C1558" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1559" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1559" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C1559" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1560" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1560" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1560" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1561" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1561" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C1561" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1562" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1562" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C1562" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1563" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1563" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C1563" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1564" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1564" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C1564" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1565" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1565" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C1565" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1566" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1566" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1566" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1567" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1567" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1567" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1568" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1568" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1568" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1569" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1569" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1569" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1570" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1570" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1570" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1571" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1571" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1571" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1572" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1572" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1572" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1573" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1573" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1573" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1574" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1574" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C1574" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1575" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1575" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C1575" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1576" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1576" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1576" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1577" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1577" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C1577" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1578" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1578" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C1578" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1579" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1579" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C1579" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1580" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1580" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1580" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1581" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1581" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C1581" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1582" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1582" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C1582" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1583" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1583" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C1583" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1584" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1584" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C1584" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1585" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1585" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C1585" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1586" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1586" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1586" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1587" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1587" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C1587" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1588" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1588" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C1588" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1589" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1589" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C1589" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1590" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1590" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C1590" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1591" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1591" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C1591" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1592" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1592" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C1592" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1593" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1593" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C1593" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1594" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1594" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C1594" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1595" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1595" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C1595" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1596" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1596" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C1596" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1597" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1597" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C1597" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1598" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1598" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C1598" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1599" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1599" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C1599" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1600" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1600" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C1600" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1601" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1601" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C1601" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1602" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1602" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C1602" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1603" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1603" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C1603" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1604" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1604" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C1604" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1605" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1605" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C1605" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1606" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1606" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C1606" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1607" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1607" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C1607" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1608" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1608" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C1608" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1609" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1609" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C1609" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1610" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1610" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1610" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1611" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1611" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C1611" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1612" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1612" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C1612" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1613" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1613" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C1613" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1614" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1614" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C1614" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1615" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1615" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C1615" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1616" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1616" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C1616" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1617" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1617" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C1617" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1618" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1618" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C1618" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1619" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1619" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C1619" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1620" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1620" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C1620" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1621" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1621" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C1621" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1622" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1622" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C1622" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1623" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1623" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C1623" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1624" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1624" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C1624" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1625" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1625" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C1625" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1626" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1626" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C1626" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1627" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1627" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C1627" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1628" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1628" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C1628" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1629" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1629" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C1629" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1630" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1630" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C1630" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1631" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1631" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C1631" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1632" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1632" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1632" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1633" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1633" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C1633" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1634" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1634" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C1634" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1635" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1635" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C1635" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1636" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1636" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1636" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1637" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1637" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C1637" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1638" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1638" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1638" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1639" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1639" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1639" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1640" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1640" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C1640" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1641" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1641" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1641" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1642" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1642" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C1642" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1643" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1643" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C1643" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1644" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1644" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C1644" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1645" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1645" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C1645" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1646" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1646" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C1646" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1647" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1647" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1647" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1648" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1648" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C1648" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1649" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1649" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C1649" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1650" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1650" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C1650" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1651" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1651" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C1651" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1652" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1652" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C1652" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1653" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1653" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1653" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1654" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1654" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1654" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1655" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1655" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C1655" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1656" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1656" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C1656" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1657" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1657" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C1657" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1658" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1658" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C1658" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1659" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1659" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C1659" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1660" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1660" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C1660" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1661" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1661" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C1661" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1662" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1662" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C1662" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1663" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1663" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C1663" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1664" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1664" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C1664" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1665" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1665" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C1665" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1666" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1666" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1666" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1667" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1667" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C1667" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1668" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1668" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C1668" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1669" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1669" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1669" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1670" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1670" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1670" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1671" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1671" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C1671" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1672" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1672" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C1672" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1673" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1673" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C1673" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1674" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1674" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C1674" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1675" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1675" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C1675" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1676" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1676" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C1676" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1677" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1677" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C1677" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1678" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1678" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C1678" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1679" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1679" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C1679" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1680" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1680" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C1680" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1681" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1681" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C1681" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1682" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1682" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C1682" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1683" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1683" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C1683" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1684" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1684" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C1684" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1685" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1685" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C1685" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1686" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1686" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C1686" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1687" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1687" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C1687" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1688" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1688" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C1688" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1689" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1689" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C1689" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1690" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1690" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C1690" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1691" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1691" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C1691" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1692" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1692" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C1692" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1693" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1693" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1693" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1694" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1694" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C1694" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1695" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1695" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C1695" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1696" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1696" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C1696" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1697" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1697" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C1697" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1698" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1698" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C1698" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1699" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1699" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C1699" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1700" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1700" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C1700" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1701" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1701" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C1701" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
